--- a/frontend/public/templates/directorio_full.xlsx
+++ b/frontend/public/templates/directorio_full.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000EA5E9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,100 +413,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:N199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>proyecto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>codigo de proyecto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tipo de sistema sistema</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>contacto de mantenimiento en sitio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>numero de contacto de mantenimiento</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Codigo de proyecto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo de sistema Sistema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Contacto de Mantenimiento en sitio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Numero de contacto de mantenimiento</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>2° nombre de contacto de mantenimiento</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2° numero de contacto de mantenimiento</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>correo de mantenimiento</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>contacto interno pm</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>numero de interno</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>nombre del cliente</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>empresa del cliente</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>numero cliente</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>correo del cliente</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>categoría</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Correo de mantenimiento</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Contacto interno PM</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Numero de interno</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Nombre del cliente</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Empresa del cliente</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Numero cliente</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Correo del cliente</t>
         </is>
       </c>
     </row>
@@ -548,19 +514,9 @@
           <t>999 105 5811</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>jtoledo@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -590,19 +546,9 @@
           <t>999 105 5811</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>jtoledo@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -632,19 +578,9 @@
           <t>999 105 5811</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>jtoledo@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -669,22 +605,14 @@
           <t>Ing. Joaquin Melendez</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>9511002051</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9511002051</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>joamelendez@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -714,19 +642,9 @@
           <t>52 9581248898</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>acamarena@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -756,19 +674,9 @@
           <t>52 9581248898</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>acamarena@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -798,16 +706,6 @@
           <t>+52 1 962 609 1617</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,19 +738,9 @@
           <t>maruiz@asur.com.mx</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>dgofpina@oma.aero</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -877,8 +765,10 @@
           <t>ing. jesus saldaña</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>6566382991</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6566382991</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -893,16 +783,6 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>jesus.hinostroza@oma.aero</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -927,8 +807,10 @@
           <t>ing. Jose Alfrado Ortiz</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>6672126891</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6672126891</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -943,16 +825,6 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>jesus.hinostroza@oma.aero</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -987,16 +859,6 @@
           <t>jesus.hinostroza@oma.aero</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1019,8 +881,10 @@
           <t>ing. Raul Flores</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>8712492923</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8712492923</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1035,16 +899,6 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>jesus.hinostroza@oma.aero</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -1084,16 +938,6 @@
           <t>jesus.hinostroza@oma.aero</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,16 +970,6 @@
           <t>jesus.hinostroza@oma.aero</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1178,11 +1012,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1235,11 +1064,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1282,11 +1106,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1329,11 +1148,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1376,11 +1190,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1423,11 +1232,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1470,11 +1274,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1517,11 +1316,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1564,11 +1358,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1611,11 +1400,6 @@
           <t>Miguel Litchi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1648,16 +1432,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1690,16 +1464,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1732,16 +1496,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1774,16 +1528,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1816,16 +1560,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1858,16 +1592,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1900,16 +1624,6 @@
           <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1942,16 +1656,6 @@
           <t>apina@axisfoster.com</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1984,16 +1688,6 @@
           <t>apina@axisfoster.com</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2026,16 +1720,6 @@
           <t>apina@axisfoster.com</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2068,19 +1752,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2115,19 +1789,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2162,19 +1826,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2209,19 +1863,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2256,19 +1900,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2303,19 +1937,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2350,19 +1974,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2397,19 +2011,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2444,19 +2048,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2491,19 +2085,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2538,19 +2122,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2585,19 +2159,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2632,19 +2196,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2679,19 +2233,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2726,19 +2270,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2773,19 +2307,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2820,19 +2344,9 @@
           <t>alejandro.hernandez@la-rainmakers.com</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>alejandro.hernandez@la-rainmakers.com</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -2867,16 +2381,6 @@
           <t>m.cid@centromedicodetoluca.com.mx</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2909,16 +2413,6 @@
           <t>m.cid@centromedicodetoluca.com.mx</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2951,16 +2445,6 @@
           <t>m.cid@centromedicodetoluca.com.mx</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2993,16 +2477,6 @@
           <t>bsilva@totis.com.mx</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3035,16 +2509,6 @@
           <t>gnajera@mexcoat.com</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3077,16 +2541,6 @@
           <t>gnajera@mexcoat.com</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3119,19 +2573,9 @@
           <t>MLOPEZA@gtrimex.mx</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>MLOPEZA@gtrimex.mx</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -3176,11 +2620,6 @@
           <t>mantenimiento@congelados-alysa.com.mx'</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>J. Palacios</t>
@@ -3194,11 +2633,6 @@
       <c r="N60" t="inlineStr">
         <is>
           <t>jpalacio@pbi.mx</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Cliente</t>
         </is>
       </c>
     </row>
@@ -3228,19 +2662,9 @@
           <t>55 4361 9977</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>octavio.bocanegra@merckgroup.com</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -3273,6 +2697,11 @@
       <c r="F62" t="inlineStr">
         <is>
           <t>Emilio Mujica</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>+52 1 55 9187 6571</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3282,16 +2711,6 @@
 mttocai@inred.mx</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3324,19 +2743,9 @@
           <t>j.gonzalez@trafimar.com.mx</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>j.gonzalez@trafimar.com.mx</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
@@ -3366,16 +2775,6 @@
           <t>servicios.generales@inecuh.edu.mx</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3403,16 +2802,6 @@
           <t>luis.gonzalez@aerobal.com</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3455,16 +2844,6 @@
           <t>ipasa95@hotmail.com'</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3497,16 +2876,6 @@
           <t>mendoza@meba.com.mx</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3534,16 +2903,6 @@
           <t>elopeza@antea.mx</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3571,16 +2930,6 @@
           <t>roger.montoya@hologic.com</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3619,16 +2968,6 @@
 mayalaj@elpalaciodehierro.onmicrosoft.com</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3661,16 +3000,6 @@
           <t>octavio@cesloleasing.com</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3713,16 +3042,6 @@
           <t>operacion@foadmi.com</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3750,16 +3069,6 @@
           <t>bijuarez@zonte.com.mx</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3792,16 +3101,6 @@
           <t>rbachtold@royal-holiday.com</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3824,17 +3123,9 @@
           <t>Contadora Patricia</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>7797962249</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>7797962249</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3155,6 @@
           <t>55 1853 4601</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3901,31 +3182,21 @@
           <t>55 1853 4601</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>55 1853 4601</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Villa Verde</t>
+          <t>Aquamatic División Del Norte</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INDO-MID01-FV05020</t>
+          <t>INDO-EDO04-FV05017</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3933,41 +3204,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Mercedez Cruz</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>+52 55 1079 8357</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>mcruz@decumerida.com</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ing. Miguel Reyes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>55 1853 4601</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jose A. Fndez - Paseo Reforma</t>
+          <t>Interaqua Qro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INDO-CMX12-FV05028</t>
+          <t>INDO-QRO01-FV05016</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3977,34 +3233,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Patricia Espindola</t>
+          <t>Edith Calixto</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>+52 1 55 5402 4991</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>446 141 3449</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>juancarlos@natacioninteraqua.com</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Juan Carlos de la Fuente</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>55 2898 5974</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>juancarlos@natacioninteraqua.com</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hector Flores-club de golf</t>
+          <t>Bernardo Quintana</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>INDO-CMX20-FV05039</t>
+          <t>INDO-EDO05-FV05019</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4014,32 +3280,39 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Roberto flores</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>5537245607</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Bernardo Quintana</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>5591079790</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bernardo Quintana</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>5591079790</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>bernardo.quintana@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hector Flores</t>
+          <t>Villa Verde</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INDO-EDO09-FV05038</t>
+          <t>INDO-MID01-FV05020</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4047,49 +3320,31 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Lazaro Arroyo</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>5574741735</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Héctor Flores</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>5541352129</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>hectorf@promac1.com.mx</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mercedez Cruz</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>+52 55 1079 8357</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>mcruz@decumerida.com</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Guillermo Ballesteros</t>
+          <t>Sergio Vela - Cedral</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INDO-CMX19-FV05037</t>
+          <t>INDO-CMX09-FV05023</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4099,34 +3354,44 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Guillermo Ballesteros</t>
+          <t>Sergion Vela</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>+52 1 55 5436 9238</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>55 4359 6496</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>sergio.vela@mac.com</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Sergion Vela</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>55 4359 6496</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>sergio.vela@mac.com</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cheval</t>
+          <t>Rafael Villalobos - Loma del rey 50</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INDO-CMX23-FV05043</t>
+          <t>INDO-CMX10-FV05024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4134,36 +3399,46 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Brenda Sánchez</t>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Rafael  Villalobos</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>55 5503 6567</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>bsanchez@chevroletvallejo.com.mx</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>villalobosrafael@me.com</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Rafael  Villalobos</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>55 5503 6567</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>villalobosrafael@me.com</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sergio Cruz - Tecolutla 386</t>
+          <t>Eduardo Arcila</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INDO-CMX26-FV05047</t>
+          <t>INDO-EDO06-FV05025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4171,41 +3446,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Biagio Lentini</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>+52 55 6974 6118</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>mantto_rc@rc.com.mx</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gabriel Morales</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>55 7970 7671</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Four Seasons Punta Mita</t>
+          <t>Miguel Irurita - Bosque alto 8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INDO-GDL01-FV05051</t>
+          <t>INDO-CMX11-FV05026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4213,41 +3473,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Hugo Contreras</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>+52 322 278 8528</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>hugo.contreras@fourseasons.com</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Miguel Irurita</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>55 1798 6977</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nuvoil Grande</t>
+          <t>Familia Treviño</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>INDO-VER01-FV05055</t>
+          <t>INDO-EDO07-FV05027</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4255,36 +3500,31 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Vicente Ferral</t>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Alejandro Treviño</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5522705218</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>vicente.ferral@nuvoil.com</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>atrevino@ayemsa.com.mx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nuvoil Chico</t>
+          <t>Jose A. Fndez - Paseo Reforma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INDO-VER02-FV05056</t>
+          <t>INDO-CMX12-FV05028</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4292,36 +3532,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Vicente Ferral</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>vicente.ferral@nuvoil.com</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Patricia Espindola</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>+52 1 55 5402 4991</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>METALITEC 3</t>
+          <t>Teresa segovia - Bosque de Pin</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INDO-HGO11-FV05066</t>
+          <t>INDO-CMX13-FV05029</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4331,34 +3561,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jesús Dan Montiel</t>
+          <t>Gabriela De Fuentes</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>771 102 3413</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>5554067945</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>METALITEC</t>
+          <t>Casa Vaca - Amanali</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>INDO-HGO11-FV05066</t>
+          <t>INDO-HGO05-FV05030</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4368,34 +3588,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Jesús Dan Montiel</t>
+          <t>Vaca</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>771 102 3413</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>5591857138</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>METALITEC 2</t>
+          <t>Alejandro Chico - Tiro al Pichón</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>INDO-HGO11-FV05066</t>
+          <t>INDO-CMX14-FV05031</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4405,34 +3615,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jesús Dan Montiel</t>
+          <t>Alejandro Chico</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>771 102 3413</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>5513532951</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Pablo Favela - Carrizal</t>
+          <t>Mauricio Porraz - Cda Transmonte 609</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INDO-CMX43-FV05072</t>
+          <t>INDO-CMX15-FV05032</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4440,36 +3640,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Pablo Favela</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>5511976362</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Porraz</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>55 3697 5595</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Pablo Favela - Carrizal 30D</t>
+          <t>Arcelia G Morton</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>INDO-EDO23-FV05073</t>
+          <t>INDO-CMX16-FV05033</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4477,36 +3667,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Pablo Favela</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>5511976362</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Gabriela Molina</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>55 9197 3542</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pablo Favela - Piamonte 1</t>
+          <t>Hector Flores-club de golf</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>INDO-MOR02-FV05074</t>
+          <t>INDO-CMX20-FV05039</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4514,36 +3694,56 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Pablo Favela</t>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Roberto flores</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>5537245607</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mariana Balcells</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>55 5195 8394</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>mbalcells@quaker-state.com.mx</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>5511976362</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+          <t>Héctor Flores</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>5541352129</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>hectorf@promac1.com.mx</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUPERVISA BOMSOR</t>
+          <t>Hector Flores</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUPO-CMX44-FV01201</t>
+          <t>INDO-EDO09-FV05038</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4553,49 +3753,54 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Javier Cadaval</t>
+          <t>Lazaro Arroyo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+52 55 5107 0025</t>
+          <t>5574741735</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Victor Eyssautier</t>
+          <t>Mariana Balcells</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>+52 55 6791 0510</t>
+          <t>55 5195 8394</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>veb@grupo-sacmag.com.mx</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>mbalcells@quaker-state.com.mx</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Héctor Flores</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>5541352129</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>hectorf@promac1.com.mx</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SUPERVISA INGENIAL</t>
+          <t>Guillermo Ballesteros</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUPO-CMX45-FV01202</t>
+          <t>INDO-CMX19-FV05037</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4605,49 +3810,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Javier Cadaval</t>
+          <t>Guillermo Ballesteros</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>+52 55 5107 0025</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Victor Eyssautier</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>+52 55 6791 0510</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>veb@grupo-sacmag.com.mx</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>55 5436 9238</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Guillermo Ballesteros</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>55 5436 9238</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>gballesterosch@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SUPERVISA JCB</t>
+          <t>Azcarraga - Ahuehuetes Norte</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUPO-CMX46-FV01203</t>
+          <t>INDO-CMX17-FV05034</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4657,49 +3852,39 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Javier Cadaval</t>
+          <t>Gerardo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+52 55 5107 0025</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Victor Eyssautier</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>+52 55 6791 0510</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>veb@grupo-sacmag.com.mx</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>55 4855 0629</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Gonzalo Azcarraga</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>55 4144 2754</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>gonzaloaz2@hotmail.com</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SUPERVISA SUPERTECNICOS</t>
+          <t>Claudia Monroy - Tiro al pichón 200</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUPO-CMX47-FV01204</t>
+          <t>INDO-CMX18-FV05036</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4709,49 +3894,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Javier Cadaval</t>
+          <t>Claudia Monroy</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+52 55 5107 0025</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Victor Eyssautier</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>+52 55 6791 0510</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>veb@grupo-sacmag.com.mx</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>55 5434 5030</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Claudia Monrroy</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>55 5434 5030</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>claudiamuriel@prodigy.net.mx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ECOFRIO P14</t>
+          <t>Eduardo Arcila-Valle de Bravo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>INDO-CMX48-FV05079</t>
+          <t>INDO-EDO08-FV05035</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4759,56 +3934,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Ángel Hernández</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>+52 771 139 4570</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>angel@solara.energy</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Pablo Rión</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>+52 1 55 1554 6883</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>pablorion@solara.energy</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Gabriel Morales</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>55 7970 7671</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLAZA UNIVERSIDAD AC</t>
+          <t>Rosa Barrena Meraz</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>INDO-AGS06-FV05082</t>
+          <t>INDO-CMX22-FV05042</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4816,41 +3961,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Laura Tello</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>gerencia@plazauniversidadags.mx</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Juan Manuel Avila</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>+52 449 106 7503</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>icardo Díaz</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>5515101424</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLAZA UNIVERSIDAD AC 3</t>
+          <t>Beatriz Escobedo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INDO-AGS04-FV05077</t>
+          <t>INDO-CMX21-FV05040</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4858,41 +3988,31 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Laura Tello</t>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Beatriz Escobedo</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>5532335449</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>gerencia@plazauniversidadags.mx</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Juan Manuel Avila</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>+52 449 106 7503</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>bescobedo@nye.com.mx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PLAZA UNIVERSIDAD AC 2</t>
+          <t>Cheval</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INDO-AGS03-FV05076</t>
+          <t>INDO-CMX23-FV05043</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4902,39 +4022,24 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laura Tello</t>
+          <t>Brenda Sánchez</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>gerencia@plazauniversidadags.mx</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Juan Manuel Avila</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>+52 449 106 7503</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>bsanchez@chevroletvallejo.com.mx</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO B1</t>
+          <t>Valentin Gari - San Miguel 39</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PRKO-EDO27-FV01401</t>
+          <t>INDO-PUE02-FV05041</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4942,51 +4047,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
+          <t>221 272 4242</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>valentingari@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO HVAC</t>
+          <t>Claudio Zapata</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PRKO-EDO28-FV01402</t>
+          <t>INDO-CMX27-FV05048</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4996,49 +4076,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
+          <t>Graciela Sanchez</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>5513305458</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO B2</t>
+          <t>Camucuato</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PRKO-EDO29-FV01403</t>
+          <t>INDO-MLM01-FV05053</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5046,51 +4101,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>davidmora01@hotmail.com</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO C</t>
+          <t>Camucuato 2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PRKO-EDO30-FV01404</t>
+          <t>INDO-MLM01-FV05053</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5098,51 +4123,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
-        </is>
-      </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>davidmora01@hotmail.com</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CENTRUMPARK EDIFICIO D</t>
+          <t>Norma Salas - Corregidora 76</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PRKO-EDO31-FV01405</t>
+          <t>INDO-CMX25-FV05045</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5150,51 +4145,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
+          <t>5555065058</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>jjrisoul@grupo-sacmag.com.mx</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO B1</t>
+          <t>Sergio Cruz - Tecolutla 386</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PRKO-EDO27-FV01401</t>
+          <t>INDO-CMX26-FV05047</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5202,51 +4172,31 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Herver López</t>
+          <t>Biagio Lentini</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>+52 55 3006 0793</t>
+          <t>+52 55 6974 6118</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>mantto_rc@rc.com.mx</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CENTRUM PARK EDIFICIO E</t>
+          <t>Miguel Vives - Bosque de Olmos</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PRKO-EDO32-FV01406</t>
+          <t>INDO-CMX24-FV05044</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5254,51 +4204,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez (cliente final)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>+52 55 6808 5888</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
-        </is>
-      </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>mickey.vives@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BIDASOA</t>
+          <t>Four Seasons Punta Mita</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INDO-EDO41-FV05106</t>
+          <t>INDO-GDL01-FV05051</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5306,51 +4226,31 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Diego Alva</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>56 3794 2332</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Javier Morales</t>
+          <t>Hugo Contreras</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>55 8124 0902</t>
+          <t>+52 322 278 8528</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>energia@bidasoa.mx</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>hugo.contreras@fourseasons.com</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TEXTURIZADOS</t>
+          <t>Nuvoil Grande</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TEXTURIZADOS</t>
+          <t>INDO-VER01-FV05055</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5360,39 +4260,24 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Eduardo Gonzalez</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>56 2792 1233</t>
+          <t>Vicente Ferral</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>mantenimientow@tytwindsor.com</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>vicente.ferral@nuvoil.com</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DULCES MODELO 1</t>
+          <t>Nuvoil Chico</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DULCES MODELO 1</t>
+          <t>INDO-VER02-FV05056</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5400,31 +4285,26 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Juan Manuel Avila</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>+52 449 106 7503</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Vicente Ferral</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>vicente.ferral@nuvoil.com</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DULCES MODELO 2</t>
+          <t>Guillermo Díaz - Cocoyoles</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DULCES MODELO 2</t>
+          <t>INDO-YUC01-FV05046</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5432,31 +4312,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Juan Manuel Avila</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>+52 449 106 7503</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>999 949 3176</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AGROBAL ESTABLO</t>
+          <t>Manuel Pacheco - Rancho la Cam</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>INDO-GTO03-FV05104</t>
+          <t>INDO-EDO10-FV05050</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5464,36 +4334,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Aarón Alonso Agrobal</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>52  429 119 1556</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>55 1474 9543</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AGROBAL ORDEÑA</t>
+          <t>Paliza - Acapulco</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>INDO-GTO04-FV05105</t>
+          <t>INDO-GRO01-FV05049</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5501,36 +4356,21 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Aarón Alonso Agrobal</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>52  429 119 1556</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>5560889910</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Artículos Higiénicos De México SA DE CV</t>
+          <t>Juan Carlos Hernaiz Vigil</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INDO-EDO01-FV05007</t>
+          <t>INDO-MOR01-FV05052</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5538,1679 +4378,2822 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Edgar González</t>
-        </is>
-      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>+52 1 55 6706 5009</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>egonzalez@articuloshigienicos.com</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Alejandro Tecalco</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>atecalco@articuloshigienicos.com</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>Cliente</t>
+          <t>5554083591</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>METALITEC 3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ASRO-CUN01-BT00101</t>
+          <t>INDO-HGO11-FV05066</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Jesús Dan Montiel</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>771 102 3413</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>METALITEC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ASRO-CUN02-BT00102</t>
+          <t>INDO-HGO11-FV05066</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Jesús Dan Montiel</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>771 102 3413</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>METALITEC 2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ASRO-CUN03-BT00103</t>
+          <t>INDO-HGO11-FV05066</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Jesús Dan Montiel</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>771 102 3413</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sala Bravo T2</t>
+          <t>Pablo Favela - Carrizal</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ASRO-CUN04-BT00104</t>
+          <t>INDO-CMX43-FV05072</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Pablo Favela</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>5511976362</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>JJ Risoul - Sistema Risco 431</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ASRO-CUN05-BT00105</t>
+          <t>INDO-CMX39-FV05061</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>5555065058</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Julio Kuri-Tlapexco 203</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ASRO-CUN06-BT00106</t>
+          <t>INDO-CMX40-FV05062</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>5554070656</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBO</t>
+          <t>Pablo Favela - Carrizal 30D</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ASRO-CUN07-BT00107</t>
+          <t>INDO-EDO23-FV05073</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Pablo Favela</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>5511976362</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PTAR</t>
+          <t>Pablo Favela - Piamonte 1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ASRO-CUN08-BT00108</t>
+          <t>INDO-MOR02-FV05074</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Pablo Favela</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>5511976362</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Almacén General</t>
+          <t>Altadena</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ASRO-CUN09-BT00109</t>
+          <t>INDO-CMX41-FV05070</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>55 6817 3944</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Comedor</t>
+          <t>Luisa Riba</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ASRO-CUN10-BT00110</t>
+          <t>INDO-HGO13-FV05068</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>José Luis Rivera</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>998 147 3974</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>55 4192 4241</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Hidro</t>
+          <t>SUPERVISA BOMSOR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ASRO-CUN11-BT00111</t>
+          <t>SUPO-CMX44-FV01201</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Javier Cadaval</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>+52 55 5107 0025</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>José Luis Rivera</t>
+          <t>Victor Eyssautier</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>998 147 3974</t>
+          <t>+52 55 6791 0510</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>veb@grupo-sacmag.com.mx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>SUPERVISA INGENIAL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ASRO-CUN12-BT00112</t>
+          <t>SUPO-CMX45-FV01202</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Javier Cadaval</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>+52 55 5107 0025</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>José Luis Rivera</t>
+          <t>Victor Eyssautier</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>998 147 3974</t>
+          <t>+52 55 6791 0510</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>jtorres@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Josue jonathan Reyes Anquino</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>5669902972</v>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>veb@grupo-sacmag.com.mx</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MERIDA</t>
+          <t>SUPERVISA JCB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ASRO-MID02-BT00113</t>
+          <t>SUPO-CMX46-FV01203</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ing. José Toledo</t>
+          <t>Javier Cadaval</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>999 105 5811</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Jose Manuel canche</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>9996020707</v>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>jtoledo@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>+52 55 5107 0025</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Victor Eyssautier</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>+52 55 6791 0510</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>veb@grupo-sacmag.com.mx</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>SUPERVISA SUPERTECNICOS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ASRO-VER03-BT00114</t>
+          <t>SUPO-CMX47-FV01204</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Javier Cadaval</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>+52 55 5107 0025</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Marcos jefe</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>2299048869</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Alan Josep Jamies</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>5666825786</v>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Victor Eyssautier</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>+52 55 6791 0510</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>veb@grupo-sacmag.com.mx</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HUATULCO</t>
+          <t>ECOFRIO P14</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ASRO-HUX01-BT00115</t>
+          <t>INDO-CMX48-FV05079</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>IVAN</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>52 9581248898</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Camacho</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>9211503420</v>
+          <t>Ángel Hernández</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>+52 771 139 4570</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>angel@solara.energy</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Pablo Rión</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>+52 1 55 1554 6883</t>
+        </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>acamarena@asur.com.mx</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>pablorion@solara.energy</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MINATITLAN</t>
+          <t>PLAZA UNIVERSIDAD AC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ASRO-MTT01-BT00116</t>
+          <t>INDO-AGS06-FV05082</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Erik Fernadez Bandala</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>229 771 6905</t>
+          <t>Laura Tello</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>jpereyra@asur.com.mx</t>
+          <t>gerencia@plazauniversidadags.mx</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Alan Josep Jamies</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>5666825786</v>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Juan Manuel Avila</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>+52 449 106 7503</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CULIACAN</t>
+          <t>PLAZA UNIVERSIDAD AC 3</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OMAO-CUL01-BT00201</t>
+          <t>INDO-AGS04-FV05077</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Alfredo (Jefe Mtto)</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>6672126891</v>
+          <t>Laura Tello</t>
+        </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>culjortiz@oma.aero</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>gerencia@plazauniversidadags.mx</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Juan Manuel Avila</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>+52 449 106 7503</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MONTERREY</t>
+          <t>PLAZA UNIVERSIDAD AC 2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>OMAO-MTY01-BT00202</t>
+          <t>INDO-AGS03-FV05076</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Luis aguirre</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>9212015402</v>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Laura Tello</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>gerencia@plazauniversidadags.mx</t>
+        </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Armando Angel</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>8662050572</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Juan Manuel Avila</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>+52 449 106 7503</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ACAPULCO</t>
+          <t>CENTRUM PARK EDIFICIO B1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>OMAO-ACA01-BT00203</t>
+          <t>PRKO-EDO27-FV01401</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Felipe Mantto</t>
+          <t>Eduardo Gonzalez (cliente final)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>744 431 0208</t>
+          <t>+52 55 6808 5888</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ing Carlos Mantto</t>
+          <t>Herver López</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>744 100 9324</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>CENTRUM PARK EDIFICIO HVAC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>OMAO-CJS01-BT00204</t>
+          <t>PRKO-EDO28-FV01402</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Eduardo Santana</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>+52 636 124 2211</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez (cliente final)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>+52 55 6808 5888</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CHIHUAHUA CHICO</t>
+          <t>CENTRUM PARK EDIFICIO B2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OMAO-CUU01-BT00205</t>
+          <t>PRKO-EDO29-FV01403</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez (cliente final)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>+52 55 6808 5888</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Abiel</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>6141982637</v>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CHIHUAHUA GRANDE</t>
+          <t>CENTRUM PARK EDIFICIO C</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OMAO-CUU02-BT00206</t>
+          <t>PRKO-EDO30-FV01404</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez (cliente final)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>+52 55 6808 5888</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Abiel</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>6141982637</v>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ZIHUATANEJO</t>
+          <t>CENTRUMPARK EDIFICIO D</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OMAO-ZIH01-BT00207</t>
+          <t>PRKO-EDO31-FV01405</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Alejandro jefe mtto</t>
+          <t>Eduardo Gonzalez (cliente final)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>755 130 6634</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>+52 55 6808 5888</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>CENTRUM PARK EDIFICIO B1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OMAO-REX01-BT00208</t>
+          <t>PRKO-EDO27-FV01401</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez (cliente final)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>+52 55 6808 5888</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Joel Serrano Jefe Mantto</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>8999564553</v>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TORREON</t>
+          <t>CENTRUM PARK EDIFICIO E</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OMAO-TRC01-BT00209</t>
+          <t>PRKO-EDO32-FV01406</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez (cliente final)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>+52 55 6808 5888</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Raul jefe mtto</t>
+          <t>Herver López</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>871 249 2923</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>BIDASOA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OMAO-DGO01-BT00210</t>
+          <t>INDO-EDO41-FV05106</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Abel</t>
+          <t>Diego Alva</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>+52 1 618 109 7872</t>
+          <t>56 3794 2332</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>6181447252</v>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Javier Morales</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>55 8124 0902</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>energia@bidasoa.mx</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>CLARIMEX</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OMAO-ZAC01-BT00211</t>
+          <t>CLARIMEX</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Nelson jefe mtto</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>492 146 7276</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ver - Bca del Rio</t>
+          <t>TEXTURIZADOS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FTMO-VER04-HB00326</t>
+          <t>TEXTURIZADOS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Alan Josep Jamies</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>5666825786</v>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>56 2792 1233</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>mantenimientow@tytwindsor.com</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALYSA</t>
+          <t>CODIGO FOODS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>INDO-HGO01-HB05001</t>
+          <t>CODIGO FOODS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Elias Gonzales</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>5530444159</v>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Victor Martinez</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>55 1470 0741</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>vmartinez@codigofoods.com.mx</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DISEKO</t>
+          <t>BOLSAS ARTESANALES 2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>INDO-AGS01-BT05002</t>
+          <t>BOLSAS ARTESANALES 2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Eloi Ruiz</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>4651055253</v>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Marco jefe de mtto</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>+52 1 449 144 1392</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VITROGENERA</t>
+          <t>BOLSAS ARTESANALES 3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>INDO-CMX01-HB05003</t>
+          <t>BOLSAS ARTESANALES 3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>David Torres Vidal</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>5541863674</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Marco jefe de mtto</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>+52 1 449 144 1392</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BOCAR</t>
+          <t>DULCES MODELO 1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>INDO-CMX02-BT05004</t>
+          <t>DULCES MODELO 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Julio Gonzalez Bocar</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>55 1189 0184</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Juan Manuel Avila</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>+52 449 106 7503</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>REGIOPET</t>
+          <t>DULCES MODELO 2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>INDO-NLE01-BT05005</t>
+          <t>DULCES MODELO 2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Jesús Lozada</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>81 1754 7822</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>jlozadaglez@regiopet.com</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Armando Angel</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
-        <v>8662050572</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Juan Manuel Avila</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>+52 449 106 7503</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BROM</t>
+          <t>CEDICER</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>INDO-CMX28-BT05058</t>
+          <t>CEDICER</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>José Luis Lira</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>+52 55 4005 3219</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hilda Velasco</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>hvelasco@brom.com.mx</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>Arquitecto Brad</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>4741042735</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RESIDEO</t>
+          <t>BODESA - Villa de Álvarez</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>INDO-CUU03-BT05060</t>
+          <t>BODESA - Villa de Álvarez</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Yibran Macías</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>+52 614 256 7280</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Yibran.Macias@resideo.com</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>luis.macedo@bodesa.com.mx</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IPASA</t>
+          <t>BODESA - Zamora</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>INDO-AGS05-BT05080</t>
+          <t>BODESA - Zamora</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Marco jefe de mtto</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>+52 1 449 144 1392</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Paco Diaz Dri. Sunna</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>449 101 9988</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>luis.macedo@bodesa.com.mx</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Tejidos y Texturizados</t>
+          <t>BODESA - Medellín 77</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>INDO-EDO37-HB05098</t>
+          <t>BODESA - Medellín 78</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Eduardo Gonzalez</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>56 2792 1233</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>mantenimientow@tytwindsor.com</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>luis.macedo@bodesa.com.mx</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VESTA GUADALUPE</t>
+          <t>BODESA - El Porvenir</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>INDO-NLE02-BT05109</t>
+          <t>BODESA - El Porvenir</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Herver López</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>+52 55 3006 0793</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Armando Angel</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
-        <v>8662050572</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>luis.macedo@bodesa.com.mx</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>THOR</t>
+          <t>AGROBAL ESTABLO</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>INDO-SLP01-BT05110</t>
+          <t>INDO-GTO03-FV05104</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>José Daniel Ibarra</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>+52 998 291 8056</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Herver López</t>
+          <t>Aarón Alonso Agrobal</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>+52 55 3006 0793</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>herver@energiareal.mx</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>52  429 119 1556</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FRITOS TOTIS</t>
+          <t>AGROBAL ORDEÑA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>INDO-HGO06-HB05057</t>
+          <t>INDO-GTO04-FV05105</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lizbeth Silva</t>
+          <t>Aarón Alonso Agrobal</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>+52 1 55 4075 6300</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>bsilva@totis.com.mx</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Agustín Quezada</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>+52 1 771 202 9639</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>52  429 119 1556</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Artículos Higiénicos De México SA DE CV</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>INDO-EDO01-FV05007</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Adriana</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>+52 81 1531 3273</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Edgar González</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>+52 1 55 6706 5009</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>adriana.ochoa@lge.com</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Armando Angel</t>
-        </is>
-      </c>
-      <c r="J156" t="n">
-        <v>8662050572</v>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+          <t>egonzalez@articuloshigienicos.com</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Alejandro Tecalco</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>atecalco@articuloshigienicos.com</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ASRO-CUN01-BT00101</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ASRO-CUN02-BT00102</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ASRO-CUN03-BT00103</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sala Bravo T2</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ASRO-CUN04-BT00104</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BHS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ASRO-CUN05-BT00105</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ASRO-CUN06-BT00106</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>FBO</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ASRO-CUN07-BT00107</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PTAR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ASRO-CUN08-BT00108</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Almacén General</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ASRO-CUN09-BT00109</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Comedor</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ASRO-CUN10-BT00110</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Hidro</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ASRO-CUN11-BT00111</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ASRO-CUN12-BT00112</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>José Luis Rivera</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>998 147 3974</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>jtorres@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Josue jonathan Reyes Anquino</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>5669902972</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MERIDA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ASRO-MID02-BT00113</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Ing. José Toledo</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>999 105 5811</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Jose Manuel canche</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>9996020707</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>jtoledo@asur.com.mx</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>VERACRUZ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ASRO-VER03-BT00114</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Marcos jefe</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2299048869</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Alan Josep Jamies</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>5666825786</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HUATULCO</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ASRO-HUX01-BT00115</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>IVAN</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>52 9581248898</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Camacho</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>9211503420</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>acamarena@asur.com.mx</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MINATITLAN</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ASRO-MTT01-BT00116</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Erik Fernadez Bandala</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>229 771 6905</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>jpereyra@asur.com.mx</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Alan Josep Jamies</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>5666825786</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CULIACAN</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>OMAO-CUL01-BT00201</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Alfredo (Jefe Mtto)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>6672126891</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>culjortiz@oma.aero</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MONTERREY</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>OMAO-MTY01-BT00202</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Luis aguirre</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>9212015402</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Armando Angel</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>8662050572</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ACAPULCO</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OMAO-ACA01-BT00203</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Felipe Mantto</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>744 431 0208</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Ing Carlos Mantto</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>744 100 9324</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>OMAO-CJS01-BT00204</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Eduardo Santana</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>+52 636 124 2211</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CHIHUAHUA CHICO</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>OMAO-CUU01-BT00205</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Abiel</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>6141982637</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CHIHUAHUA GRANDE</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>OMAO-CUU02-BT00206</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Abiel</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>6141982637</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ZIHUATANEJO</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>OMAO-ZIH01-BT00207</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Alejandro jefe mtto</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>755 130 6634</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>REYNOSA</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OMAO-REX01-BT00208</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Joel Serrano Jefe Mantto</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>8999564553</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TORREON</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OMAO-TRC01-BT00209</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Raul jefe mtto</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>871 249 2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DURANGO</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>OMAO-DGO01-BT00210</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Abel</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>+52 1 618 109 7872</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>6181447252</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ZACATECAS</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>OMAO-ZAC01-BT00211</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Nelson jefe mtto</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>492 146 7276</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ver - Bca del Rio</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FTMO-VER04-HB00326</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Alan Josep Jamies</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>5666825786</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ALYSA</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>INDO-HGO01-HB05001</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Elias Gonzales</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>5530444159</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DISEKO</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>INDO-AGS01-BT05002</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Eloi Ruiz</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>4651055253</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VITROGENERA</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>INDO-CMX01-HB05003</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>David Torres Vidal</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>5541863674</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BOCAR</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>INDO-CMX02-BT05004</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Julio Gonzalez Bocar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>55 1189 0184</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>REGIOPET</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>INDO-NLE01-BT05005</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Jesús Lozada</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>81 1754 7822</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>jlozadaglez@regiopet.com</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Armando Angel</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>8662050572</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TELAS ASTURCON</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>INDO-PUE01-BT05006</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BROM</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>INDO-CMX28-BT05058</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>José Luis Lira</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>+52 55 4005 3219</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Hilda Velasco</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>hvelasco@brom.com.mx</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>RESIDEO</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>INDO-CUU03-BT05060</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Yibran Macías</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>+52 614 256 7280</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Yibran.Macias@resideo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>IPASA</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>INDO-AGS05-BT05080</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Marco jefe de mtto</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>+52 1 449 144 1392</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Tejidos y Texturizados</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>INDO-EDO37-HB05098</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Eduardo Gonzalez</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>56 2792 1233</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>mantenimientow@tytwindsor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>VESTA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>INDO-NLE02-BT05109</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Armando Angel</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>8662050572</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>THOR</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>INDO-SLP01-BT05110</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>José Daniel Ibarra</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>+52 998 291 8056</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Herver López</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>+52 55 3006 0793</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>herver@energiareal.mx</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FRITOS TOTIS</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>INDO-HGO06-HB05057</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Lizbeth Silva</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>+52 1 55 4075 6300</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>bsilva@totis.com.mx</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Agustín Quezada</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>+52 1 771 202 9639</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>+52 81 1531 3273</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>adriana.ochoa@lge.com</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Armando Angel</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>8662050572</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>SISTEMAS ON</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>Ilse</t>
         </is>
       </c>
-      <c r="G157" t="n">
-        <v>5641687705</v>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>5641687705</t>
         </is>
       </c>
     </row>
